--- a/public/fixtures/fp-tests/8.xlsx
+++ b/public/fixtures/fp-tests/8.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10621"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://netorgft3248279.sharepoint.com/sites/asseticom/Shared Documents/General/04. Software Services/02. Live/C&amp;B - Equans Life Cycle Surveys/North Lanarkshire Schools/Data Imports M&amp;E/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexstanbury/Downloads/FP_Tests/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="8_{31C64E29-EB63-41A5-975F-7C396B08F048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7A198B87-605E-4C4C-8715-DCCECC82F091}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A68555AE-E9C9-9346-8AC7-6C126FD3E75F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A48EAFA5-5919-46F6-B884-48D13654B430}"/>
+    <workbookView xWindow="28680" yWindow="600" windowWidth="29040" windowHeight="15840" xr2:uid="{A48EAFA5-5919-46F6-B884-48D13654B430}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$D$88</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="90">
   <si>
     <t>Ground Floor</t>
   </si>
@@ -309,12 +309,6 @@
   </si>
   <si>
     <t>G19.1 - WC</t>
-  </si>
-  <si>
-    <t>Throughout</t>
-  </si>
-  <si>
-    <t>THROUGHOUT</t>
   </si>
 </sst>
 </file>
@@ -708,10 +702,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7593CF2-4956-429C-83E7-ACBA40E21FEE}">
-  <dimension ref="A1:D89"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:D88"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>2</v>
       </c>
@@ -725,7 +719,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -739,7 +733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -753,7 +747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -767,7 +761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -781,7 +775,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -795,7 +789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -809,7 +803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -823,7 +817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -837,7 +831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -851,7 +845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -865,7 +859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -879,7 +873,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -893,7 +887,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -907,7 +901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -921,7 +915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -935,7 +929,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -949,7 +943,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -963,7 +957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -977,7 +971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -991,7 +985,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -1005,7 +999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -1019,7 +1013,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -1033,7 +1027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -1047,7 +1041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -1061,7 +1055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -1075,7 +1069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>0</v>
       </c>
@@ -1089,7 +1083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -1103,7 +1097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -1117,7 +1111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +1125,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -1145,7 +1139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>0</v>
       </c>
@@ -1159,7 +1153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -1173,7 +1167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1187,7 +1181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1201,7 +1195,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1215,7 +1209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -1229,7 +1223,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -1243,7 +1237,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -1257,7 +1251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -1271,7 +1265,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -1285,7 +1279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -1299,7 +1293,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +1307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>0</v>
       </c>
@@ -1327,7 +1321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>0</v>
       </c>
@@ -1341,7 +1335,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>0</v>
       </c>
@@ -1355,7 +1349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -1369,7 +1363,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
         <v>0</v>
       </c>
@@ -1383,7 +1377,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
         <v>0</v>
       </c>
@@ -1397,7 +1391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
         <v>0</v>
       </c>
@@ -1411,7 +1405,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
         <v>0</v>
       </c>
@@ -1425,7 +1419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -1439,7 +1433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
         <v>0</v>
       </c>
@@ -1453,7 +1447,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -1467,7 +1461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
         <v>0</v>
       </c>
@@ -1481,7 +1475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
         <v>0</v>
       </c>
@@ -1495,7 +1489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -1509,7 +1503,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -1523,7 +1517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
         <v>0</v>
       </c>
@@ -1537,7 +1531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
         <v>0</v>
       </c>
@@ -1551,7 +1545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -1565,7 +1559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
         <v>0</v>
       </c>
@@ -1579,7 +1573,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -1593,7 +1587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -1607,7 +1601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -1621,7 +1615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
         <v>0</v>
       </c>
@@ -1649,7 +1643,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
         <v>0</v>
       </c>
@@ -1663,7 +1657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
         <v>0</v>
       </c>
@@ -1677,7 +1671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
         <v>0</v>
       </c>
@@ -1691,7 +1685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
         <v>0</v>
       </c>
@@ -1705,7 +1699,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
         <v>0</v>
       </c>
@@ -1719,7 +1713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
         <v>0</v>
       </c>
@@ -1733,7 +1727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
         <v>0</v>
       </c>
@@ -1747,7 +1741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
         <v>0</v>
       </c>
@@ -1761,7 +1755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
         <v>0</v>
       </c>
@@ -1775,7 +1769,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
         <v>0</v>
       </c>
@@ -1789,7 +1783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
         <v>0</v>
       </c>
@@ -1803,7 +1797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -1817,7 +1811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
         <v>0</v>
       </c>
@@ -1831,7 +1825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
         <v>0</v>
       </c>
@@ -1845,7 +1839,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
         <v>0</v>
       </c>
@@ -1859,7 +1853,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
         <v>0</v>
       </c>
@@ -1873,7 +1867,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -1887,7 +1881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
         <v>0</v>
       </c>
@@ -1901,7 +1895,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
         <v>0</v>
       </c>
@@ -1915,30 +1909,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A87" t="s">
-        <v>90</v>
-      </c>
-      <c r="B87" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="C87">
-        <v>0</v>
-      </c>
-      <c r="D87">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="B87" s="1"/>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
       <c r="B88" s="1"/>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B89" s="1"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:D89" xr:uid="{B7593CF2-4956-429C-83E7-ACBA40E21FEE}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D89">
-      <sortCondition ref="A1:A89"/>
+  <autoFilter ref="A1:D88" xr:uid="{B7593CF2-4956-429C-83E7-ACBA40E21FEE}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D88">
+      <sortCondition ref="A1:A88"/>
     </sortState>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1946,12 +1926,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="5db48b64-35f6-4468-8f7d-90ba9a0a6b12" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="28abb233-3e57-4edf-8235-d6ecf6a0ac5a">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <_x0032_026 xmlns="28abb233-3e57-4edf-8235-d6ecf6a0ac5a">false</_x0032_026>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2202,30 +2185,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="5db48b64-35f6-4468-8f7d-90ba9a0a6b12" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="28abb233-3e57-4edf-8235-d6ecf6a0ac5a">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <_x0032_026 xmlns="28abb233-3e57-4edf-8235-d6ecf6a0ac5a">false</_x0032_026>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48A80FBB-30ED-480C-A361-C1EBB5B5AE93}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F980DBA8-D26E-488F-89C6-3A72C406B70F}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5BCD3E55-FB13-4ABE-996D-A7B1E5FE83B6}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -2234,4 +2202,31 @@
     <ds:schemaRef ds:uri="28abb233-3e57-4edf-8235-d6ecf6a0ac5a"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F980DBA8-D26E-488F-89C6-3A72C406B70F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="28abb233-3e57-4edf-8235-d6ecf6a0ac5a"/>
+    <ds:schemaRef ds:uri="5db48b64-35f6-4468-8f7d-90ba9a0a6b12"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{48A80FBB-30ED-480C-A361-C1EBB5B5AE93}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>